--- a/artfynd/A 6526-2022 artfynd.xlsx
+++ b/artfynd/A 6526-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6526-2022 artfynd.xlsx
+++ b/artfynd/A 6526-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96484940</v>
+        <v>96482638</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Lycksele, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659996.0182054698</v>
+        <v>660088</v>
       </c>
       <c r="R2" t="n">
-        <v>7189113.321986939</v>
+        <v>7189015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,69 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96484939</v>
+        <v>96482628</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lycksabäcken sandtallskog, Lycksele, Ly lm</t>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659995.9728510095</v>
+        <v>659953</v>
       </c>
       <c r="R3" t="n">
-        <v>7189114.173936105</v>
+        <v>7189132</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +840,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,19 +857,517 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96484940</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>659996</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7189113</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Carl Jansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96482609</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660020</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7189057</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avvikande färgsättning med blågröna taggar och fot, och ovansidan i grönt och lila.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96484939</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>659996</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7189114</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96482623</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660031</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7189052</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96482611</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lycksabäcken sandtallskog, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>659985</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7189102</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Ingalill  Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6526-2022 artfynd.xlsx
+++ b/artfynd/A 6526-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484940</t>
         </is>
       </c>
     </row>
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96484939</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,8 +1403,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96482611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>